--- a/legal_forms/013_lease_agreement_for_operators--legal_forms.xlsx
+++ b/legal_forms/013_lease_agreement_for_operators--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lease_agreement_for_operators_form_template</t>
+          <t>operator_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lease_agreement_for_operators_form_template</t>
+          <t>Operator Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>operator_details</t>
+          <t>operator_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>operator_details</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>property_details</t>
+          <t>property_address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>property_details</t>
+          <t>Property Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lease_start_date</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lease_start_date</t>
+          <t>Property Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,41 +612,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>lease_start_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>Start Date of Lease</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lease_amount</t>
+          <t>lease_end_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lease_amount</t>
+          <t>End Date of Lease</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>lease_amount</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>Lease Amount</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rent_payment_frequency</t>
+          <t>payment_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rent_payment_frequency</t>
+          <t>Rent Payment Frequency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>operator_payment_method</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>operator_payment_method</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>operator_insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>Operator Insurance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>operator_maintenance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>Operator Maintenance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>property_insurance</t>
+          <t>Property Insurance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,156 +796,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>property_maintenance</t>
+          <t>operator_payment_details</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>property_maintenance</t>
+          <t>Operator Payment Details</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>lease_agreement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lease_end_date</t>
+          <t>Lease Agreement</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rent_amount</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rent_amount</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>payment_terms</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>payment_terms</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lease_agreement</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>lease_agreement</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>operator_payment_details</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>operator_payment_details</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>property_insurance</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>property_insurance</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -960,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,204 +873,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>operator_details_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>operator_details_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rent_payment_frequency_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rent_payment_frequency_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rent_payment_frequency_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>operator_payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>operator_payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>property_insurance_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>property_insurance_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lease_agreement_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lease_agreement_choices</t>
+          <t>operator_insurance_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>property_insurance_choices</t>
+          <t>operator_insurance_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1082,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>property_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lease_agreement_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lease_agreement_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
